--- a/guides/qualification/DEPLOYMENT_SMOKE.xlsx
+++ b/guides/qualification/DEPLOYMENT_SMOKE.xlsx
@@ -53,7 +53,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -85,53 +85,53 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREPARING</t>
+          <t xml:space="preserve">RESTORED AFTER AUTHORIZED WIPE</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prepare Firebase prerequisites and four distinguishable images; preserve configuration snapshot privately.</t>
+          <t xml:space="preserve">Production JSON baseline reloaded. Real Firebase Auth Test passed; firebase-smoke-fixture.py stages active Firebase/readiness as a smoke prerequisite. Browser Message Test is NOT RUN by this fixture.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registration + photo</t>
+          <t xml:space="preserve">Seed / indexes</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT RUN</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normal non-demo UI; retain profile.</t>
+          <t xml:space="preserve">All 40 seed baselines reviewed; 150 bootstrap index definitions verified on VMware. Fresh isolated Mongo index tests passed.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Profile update + new photo</t>
+          <t xml:space="preserve">Registration + photo</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT RUN</t>
+          <t xml:space="preserve">USER RETEST PENDING</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reopen and inspect saved image.</t>
+          <t xml:space="preserve">Earlier production image failure: missing media.read in retained DB. Fresh seed contains all 50 policies. User controls browser; no UI PASS claimed.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Event + image</t>
+          <t xml:space="preserve">Profile update + new photo</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -141,14 +141,14 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create through UI; list/detail image checks.</t>
+          <t xml:space="preserve">Reopen and inspect saved image.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asset + image</t>
+          <t xml:space="preserve">Event + image</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -165,7 +165,7 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal retained controls</t>
+          <t xml:space="preserve">Asset + image</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -175,45 +175,62 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store exact record IDs/content/image hashes for upcoming release update.</t>
+          <t xml:space="preserve">Create through UI; list/detail image checks.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post-release preservation</t>
+          <t xml:space="preserve">Seal retained controls</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING RELEASE</t>
+          <t xml:space="preserve">NOT RUN</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">After Asset QA, GitHub release/tag then stack update; verify retained controls.</t>
+          <t xml:space="preserve">Store exact record IDs/content/image hashes for upcoming release update.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Post-release preservation</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING RELEASE</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After Asset QA, GitHub release/tag then stack update; verify retained controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cleanup</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">DEFERRED BY USER</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Keep owned smoke records through release update.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9"/>
+  <autoFilter ref="A1:C10"/>
 </worksheet>
 </file>